--- a/Team-Data/2013-14/3-24-2013-14.xlsx
+++ b/Team-Data/2013-14/3-24-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" t="n">
         <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>0.449</v>
+        <v>0.456</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>81.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
         <v>9.6</v>
@@ -691,28 +758,28 @@
         <v>25.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S2" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T2" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="V2" t="n">
         <v>15.3</v>
@@ -721,25 +788,25 @@
         <v>8.5</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z2" t="n">
         <v>19.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.5</v>
+        <v>101.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -751,7 +818,7 @@
         <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -772,19 +839,19 @@
         <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -808,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -945,7 +1012,7 @@
         <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
         <v>19</v>
@@ -966,7 +1033,7 @@
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
@@ -975,7 +1042,7 @@
         <v>23</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>25</v>
@@ -993,7 +1060,7 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
         <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.536</v>
+        <v>0.544</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I4" t="n">
         <v>35.5</v>
       </c>
       <c r="J4" t="n">
-        <v>78.2</v>
+        <v>78</v>
       </c>
       <c r="K4" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="O4" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.76</v>
+        <v>0.757</v>
       </c>
       <c r="R4" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
         <v>14.3</v>
@@ -1100,22 +1167,22 @@
         <v>98.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,28 +1191,28 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
       </c>
       <c r="AM4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1154,10 +1221,10 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>7</v>
@@ -1172,10 +1239,10 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -1207,70 +1274,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" t="n">
         <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>0.479</v>
+        <v>0.486</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O5" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P5" t="n">
         <v>24.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T5" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="W5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X5" t="n">
         <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z5" t="n">
         <v>18.3</v>
@@ -1279,13 +1346,13 @@
         <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>14</v>
@@ -1330,13 +1397,13 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,13 +1415,13 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
         <v>25</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1456,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
         <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J6" t="n">
         <v>80.3</v>
@@ -1419,22 +1486,22 @@
         <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P6" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S6" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T6" t="n">
         <v>44.7</v>
@@ -1443,13 +1510,13 @@
         <v>22.3</v>
       </c>
       <c r="V6" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>6.2</v>
@@ -1461,13 +1528,13 @@
         <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1503,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
@@ -1512,7 +1579,7 @@
         <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1521,7 +1588,7 @@
         <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
@@ -1682,7 +1749,7 @@
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP7" t="n">
         <v>19</v>
@@ -1700,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -1843,13 +1910,13 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1858,7 +1925,7 @@
         <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
         <v>3</v>
@@ -1900,7 +1967,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -1935,52 +2002,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
         <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>0.451</v>
+        <v>0.457</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J9" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L9" t="n">
         <v>8.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="N9" t="n">
         <v>0.361</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="R9" t="n">
         <v>12.3</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T9" t="n">
         <v>45.3</v>
@@ -1995,7 +2062,7 @@
         <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y9" t="n">
         <v>5.6</v>
@@ -2004,16 +2071,16 @@
         <v>22.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.8</v>
+        <v>103.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2034,16 +2101,16 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>9</v>
       </c>
       <c r="AM9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2061,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.371</v>
+        <v>0.362</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>86.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="K10" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
         <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.318</v>
+        <v>0.316</v>
       </c>
       <c r="O10" t="n">
         <v>16.9</v>
       </c>
       <c r="P10" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q10" t="n">
         <v>0.666</v>
@@ -2162,22 +2229,22 @@
         <v>14.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="U10" t="n">
         <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
         <v>8.6</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
         <v>4.9</v>
@@ -2189,13 +2256,13 @@
         <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>101</v>
+        <v>100.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>28</v>
@@ -2228,7 +2295,7 @@
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP10" t="n">
         <v>6</v>
@@ -2246,13 +2313,13 @@
         <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -2267,7 +2334,7 @@
         <v>14</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -2389,10 +2456,10 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>7</v>
@@ -2407,16 +2474,16 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR11" t="n">
         <v>18</v>
@@ -2425,10 +2492,10 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
         <v>23</v>
@@ -2437,7 +2504,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2449,7 +2516,7 @@
         <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2511,16 +2578,16 @@
         <v>26.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O12" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="P12" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.701</v>
+        <v>0.703</v>
       </c>
       <c r="R12" t="n">
         <v>11.1</v>
@@ -2535,7 +2602,7 @@
         <v>21.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
         <v>7.5</v>
@@ -2547,19 +2614,19 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.8</v>
+        <v>106.9</v>
       </c>
       <c r="AC12" t="n">
         <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -2663,34 +2730,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
         <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>0.718</v>
+        <v>0.729</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N13" t="n">
         <v>0.35</v>
@@ -2702,10 +2769,10 @@
         <v>23.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
         <v>35</v>
@@ -2714,10 +2781,10 @@
         <v>45.3</v>
       </c>
       <c r="U13" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2732,19 +2799,19 @@
         <v>20.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>3</v>
@@ -2765,7 +2832,7 @@
         <v>14</v>
       </c>
       <c r="AL13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
         <v>24</v>
@@ -2795,13 +2862,13 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
         <v>13</v>
@@ -2813,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -2845,22 +2912,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
         <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>0.704</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J14" t="n">
         <v>82.3</v>
@@ -2872,10 +2939,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O14" t="n">
         <v>21</v>
@@ -2884,7 +2951,7 @@
         <v>28.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="R14" t="n">
         <v>10.4</v>
@@ -2896,7 +2963,7 @@
         <v>42.9</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V14" t="n">
         <v>13.9</v>
@@ -2917,13 +2984,13 @@
         <v>23.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.5</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2938,7 +3005,7 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
@@ -2950,7 +3017,7 @@
         <v>13</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
         <v>22</v>
@@ -2980,10 +3047,10 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3126,10 +3193,10 @@
         <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3150,7 +3217,7 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
         <v>23</v>
@@ -3165,7 +3232,7 @@
         <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -3209,55 +3276,55 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
         <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M16" t="n">
         <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P16" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R16" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S16" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U16" t="n">
         <v>21.6</v>
@@ -3266,7 +3333,7 @@
         <v>13.7</v>
       </c>
       <c r="W16" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X16" t="n">
         <v>4.7</v>
@@ -3278,19 +3345,19 @@
         <v>19.4</v>
       </c>
       <c r="AA16" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD16" t="n">
         <v>19</v>
       </c>
-      <c r="AB16" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>15</v>
-      </c>
       <c r="AE16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
@@ -3302,7 +3369,7 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3317,10 +3384,10 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
         <v>28</v>
@@ -3329,13 +3396,13 @@
         <v>22</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3347,10 +3414,10 @@
         <v>14</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>6</v>
@@ -3359,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.696</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,46 +3476,46 @@
         <v>38.9</v>
       </c>
       <c r="J17" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.505</v>
+        <v>0.506</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
         <v>0.368</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
         <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R17" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T17" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X17" t="n">
         <v>4.6</v>
@@ -3457,19 +3524,19 @@
         <v>3.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.4</v>
+        <v>103.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3481,7 +3548,7 @@
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
         <v>8</v>
@@ -3496,10 +3563,10 @@
         <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
@@ -3520,10 +3587,10 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
@@ -3541,10 +3608,10 @@
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -3573,46 +3640,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>0.183</v>
+        <v>0.186</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J18" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N18" t="n">
         <v>0.353</v>
       </c>
       <c r="O18" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P18" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R18" t="n">
         <v>11.8</v>
@@ -3624,16 +3691,16 @@
         <v>41.2</v>
       </c>
       <c r="U18" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V18" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W18" t="n">
         <v>6.7</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
         <v>5.2</v>
@@ -3642,16 +3709,16 @@
         <v>21.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,16 +3748,16 @@
         <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
@@ -3699,7 +3766,7 @@
         <v>29</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
         <v>34</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J19" t="n">
         <v>87.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L19" t="n">
         <v>7.5</v>
@@ -3785,13 +3852,13 @@
         <v>21.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="P19" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="n">
         <v>0.78</v>
@@ -3800,7 +3867,7 @@
         <v>12.7</v>
       </c>
       <c r="S19" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
         <v>44.9</v>
@@ -3809,7 +3876,7 @@
         <v>23.4</v>
       </c>
       <c r="V19" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W19" t="n">
         <v>8.6</v>
@@ -3821,25 +3888,25 @@
         <v>5.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.3</v>
+        <v>106.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -3860,7 +3927,7 @@
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
@@ -3878,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
         <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.429</v>
+        <v>0.42</v>
       </c>
       <c r="H20" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I20" t="n">
         <v>38.1</v>
       </c>
       <c r="J20" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
         <v>0.46</v>
@@ -3967,31 +4034,31 @@
         <v>15.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O20" t="n">
         <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R20" t="n">
         <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W20" t="n">
         <v>8</v>
@@ -4009,13 +4076,13 @@
         <v>20.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4027,13 +4094,13 @@
         <v>20</v>
       </c>
       <c r="AH20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AI20" t="n">
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>13</v>
@@ -4060,7 +4127,7 @@
         <v>11</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
         <v>22</v>
@@ -4090,7 +4157,7 @@
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4218,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4227,16 +4294,16 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP21" t="n">
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4269,7 +4336,7 @@
         <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F22" t="n">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>0.743</v>
+        <v>0.739</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J22" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K22" t="n">
         <v>0.471</v>
@@ -4331,55 +4398,55 @@
         <v>22.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S22" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T22" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U22" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
         <v>6.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>106</v>
+        <v>105.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,10 +4461,10 @@
         <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4421,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4430,13 +4497,13 @@
         <v>2</v>
       </c>
       <c r="AU22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4652,7 @@
         <v>22</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4609,10 +4676,10 @@
         <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4627,7 +4694,7 @@
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" t="n">
-        <v>0.211</v>
+        <v>0.214</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
@@ -4689,28 +4756,28 @@
         <v>0.429</v>
       </c>
       <c r="L24" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M24" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.305</v>
+        <v>0.304</v>
       </c>
       <c r="O24" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.71</v>
+        <v>0.713</v>
       </c>
       <c r="R24" t="n">
         <v>12</v>
       </c>
       <c r="S24" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T24" t="n">
         <v>43.5</v>
@@ -4722,7 +4789,7 @@
         <v>17.2</v>
       </c>
       <c r="W24" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
@@ -4731,19 +4798,19 @@
         <v>7.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-11.4</v>
+        <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,10 +4822,10 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
@@ -4767,16 +4834,16 @@
         <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN24" t="n">
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>16</v>
@@ -4788,13 +4855,13 @@
         <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT24" t="n">
         <v>12</v>
       </c>
       <c r="AU24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4809,13 +4876,13 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
         <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.592</v>
+        <v>0.586</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,28 +4932,28 @@
         <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K25" t="n">
         <v>0.463</v>
       </c>
       <c r="L25" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="O25" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P25" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R25" t="n">
         <v>11.4</v>
@@ -4895,19 +4962,19 @@
         <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U25" t="n">
         <v>19.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W25" t="n">
         <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y25" t="n">
         <v>4.1</v>
@@ -4922,19 +4989,19 @@
         <v>105.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
         <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4943,31 +5010,31 @@
         <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
         <v>7</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4979,7 +5046,7 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
@@ -4991,7 +5058,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" t="n">
         <v>45</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>0.634</v>
+        <v>0.643</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="J26" t="n">
-        <v>87.3</v>
+        <v>87.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
         <v>9.5</v>
       </c>
       <c r="M26" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O26" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P26" t="n">
         <v>23.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.819</v>
       </c>
       <c r="R26" t="n">
         <v>12.6</v>
@@ -5077,7 +5144,7 @@
         <v>33.6</v>
       </c>
       <c r="T26" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="U26" t="n">
         <v>23.2</v>
@@ -5089,25 +5156,25 @@
         <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
         <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.3</v>
+        <v>107.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>3</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>2</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
@@ -5310,7 +5377,7 @@
         <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5364,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="L28" t="n">
         <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.398</v>
+        <v>0.397</v>
       </c>
       <c r="O28" t="n">
         <v>16</v>
@@ -5435,13 +5502,13 @@
         <v>0.787</v>
       </c>
       <c r="R28" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S28" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T28" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U28" t="n">
         <v>25.2</v>
@@ -5459,19 +5526,19 @@
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.3</v>
+        <v>105.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5531,7 +5598,7 @@
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
         <v>12</v>
@@ -5677,7 +5744,7 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5698,16 +5765,16 @@
         <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW29" t="n">
         <v>22</v>
@@ -5725,7 +5792,7 @@
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
         <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G30" t="n">
-        <v>0.324</v>
+        <v>0.329</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5784,34 +5851,34 @@
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O30" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P30" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T30" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U30" t="n">
         <v>19.9</v>
       </c>
       <c r="V30" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
         <v>6.8</v>
@@ -5820,10 +5887,10 @@
         <v>4.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA30" t="n">
         <v>20.3</v>
@@ -5832,22 +5899,22 @@
         <v>94.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.8</v>
+        <v>-6.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
       </c>
       <c r="AF30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH30" t="n">
         <v>27</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>28</v>
       </c>
       <c r="AI30" t="n">
         <v>28</v>
@@ -5859,13 +5926,13 @@
         <v>23</v>
       </c>
       <c r="AL30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="n">
         <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
         <v>25</v>
@@ -5880,7 +5947,7 @@
         <v>20</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6038,7 +6105,7 @@
         <v>6</v>
       </c>
       <c r="AK31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
         <v>14</v>
@@ -6059,7 +6126,7 @@
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
         <v>19</v>
@@ -6071,13 +6138,13 @@
         <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-24-2013-14</t>
+          <t>2014-03-24</t>
         </is>
       </c>
     </row>
